--- a/crosswalk/xlsx/hs-world-history__primary-source-crosswalk.xlsx
+++ b/crosswalk/xlsx/hs-world-history__primary-source-crosswalk.xlsx
@@ -31,7 +31,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,11 +48,6 @@
         <fgColor rgb="00E6EFE4"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F6E9D6"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -66,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -75,9 +70,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -640,7 +632,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -733,7 +725,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -822,7 +814,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -911,7 +903,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1000,7 +992,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1089,7 +1081,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1178,7 +1170,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1267,7 +1259,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1356,7 +1348,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1453,7 +1445,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1546,7 +1538,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1639,7 +1631,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1732,7 +1724,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1825,7 +1817,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -1918,7 +1910,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2011,7 +2003,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2104,7 +2096,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2197,7 +2189,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2290,7 +2282,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2387,7 +2379,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2480,7 +2472,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2577,7 +2569,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2670,7 +2662,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2763,7 +2755,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2860,7 +2852,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -2953,7 +2945,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3046,7 +3038,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3139,7 +3131,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3232,7 +3224,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3325,7 +3317,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3418,7 +3410,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3511,7 +3503,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -3608,7 +3600,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -3701,7 +3693,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -3794,7 +3786,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -3887,7 +3879,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -3976,7 +3968,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4065,7 +4057,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4162,7 +4154,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4255,7 +4247,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4348,7 +4340,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -4441,7 +4433,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -4534,7 +4526,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -4627,7 +4619,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -4720,7 +4712,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -4813,7 +4805,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -4906,7 +4898,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -4999,7 +4991,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5092,7 +5084,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5189,7 +5181,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -5282,7 +5274,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -5375,7 +5367,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -5468,7 +5460,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -5561,7 +5553,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -5654,7 +5646,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -5751,7 +5743,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -5844,7 +5836,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -5937,7 +5929,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6030,7 +6022,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -6123,7 +6115,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -6216,7 +6208,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -6309,7 +6301,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -6402,7 +6394,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -6495,7 +6487,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -6588,7 +6580,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -6681,7 +6673,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -6774,7 +6766,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -6867,7 +6859,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -6960,7 +6952,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -7053,7 +7045,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -7146,7 +7138,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -7239,7 +7231,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -7336,7 +7328,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -7429,7 +7421,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -7522,7 +7514,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -7615,7 +7607,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -7708,7 +7700,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -7801,7 +7793,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -7894,7 +7886,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -7991,7 +7983,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -8084,7 +8076,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -8177,7 +8169,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -8270,7 +8262,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -8363,7 +8355,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -8452,7 +8444,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -8549,7 +8541,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -8642,7 +8634,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -8735,7 +8727,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -8828,7 +8820,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -8925,7 +8917,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -9022,7 +9014,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -9119,7 +9111,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -9212,7 +9204,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -9309,7 +9301,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -9406,7 +9398,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -9499,7 +9491,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -9596,7 +9588,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -9693,7 +9685,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -9786,7 +9778,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -9879,7 +9871,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -9972,7 +9964,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -10065,7 +10057,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -10154,7 +10146,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -10251,7 +10243,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -10348,7 +10340,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -10441,7 +10433,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -10534,7 +10526,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -10631,7 +10623,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -10724,7 +10716,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -10817,7 +10809,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -10910,7 +10902,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -11003,7 +10995,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -11096,7 +11088,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -11189,7 +11181,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -11282,7 +11274,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -11375,7 +11367,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -11468,7 +11460,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -11561,7 +11553,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -11654,7 +11646,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -11751,7 +11743,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -11844,7 +11836,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -11886,42 +11878,40 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Chinese Communist propaganda poster</t>
+          <t>United States Relations with China, With Special Reference to the Period 1944-1949 (the "China White Paper")</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Poster</t>
+          <t>government report</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>Chinese state artists</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>1950s-1970s</t>
-        </is>
+          <t>U.S. Department of State</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>1949</v>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>Office of the Historian, U.S. Department of State (history.state.gov)</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Chinese+Communist+propaganda+poster+Mao</t>
+          <t>https://history.state.gov/historicaldocuments/search?q=China+White+Paper+1949</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
@@ -11931,32 +11921,32 @@
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Chinese Communist propaganda poster. Library of Congress.</t>
+          <t>U.S. Department of State, United States Relations with China, With Special Reference to the Period 1944-1949 (Washington, D.C.: Government Printing Office, 1949).</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Propaganda poster glorifying Mao and the Communist Party.</t>
+          <t>Cover and text pages of the 1949 U.S. State Department 'China White Paper' analyzing the Chinese Communist Party's rise to power and the collapse of Nationalist rule.</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>Rights caution: PRC posters likely still under copyright — verify before commercial use.</t>
-        </is>
-      </c>
-      <c r="S123" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>U.S. federal government work = public domain, so genuinely commercial-use safe. This contemporaneous State Department report documents Mao Zedong's rise and the political/economic transformation of China, directly serving W.57 without relying on a copyrighted CCP propaganda image.</t>
+        </is>
+      </c>
+      <c r="S123" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12028,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -12131,7 +12121,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -12228,7 +12218,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -12321,7 +12311,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -12414,7 +12404,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -12507,7 +12497,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -12600,7 +12590,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -12693,7 +12683,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -12786,7 +12776,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -12828,42 +12818,40 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Prague Spring, 1968</t>
+          <t>Foreign Relations of the United States, 1964-1968, Volume XVII, Eastern Europe (Czechoslovak crisis documents)</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>press photographers</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
+          <t>U.S. Department of State, Office of the Historian</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>1968</v>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>Office of the Historian, U.S. Department of State (history.state.gov)</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Prague+Spring+1968+Czechoslovakia+invasion</t>
+          <t>https://history.state.gov/historicaldocuments/search?q=Czechoslovakia+1968</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
@@ -12873,32 +12861,32 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>The Prague Spring, 1968. Library of Congress.</t>
+          <t>Foreign Relations of the United States, 1964-1968, Vol. XVII, Eastern Europe (Washington, D.C.: U.S. Government Printing Office), documents on the 1968 Soviet-led invasion of Czechoslovakia.</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>Photograph of Soviet tanks in Prague during the 1968 invasion.</t>
+          <t>U.S. diplomatic cables and memoranda from 1968 describing the Prague Spring reforms and the Warsaw Pact invasion that crushed them.</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R133" s="2" t="inlineStr">
         <is>
-          <t>Rights caution: 1968 press photos may still be under copyright — verify.</t>
-        </is>
-      </c>
-      <c r="S133" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>FRUS is a U.S. government publication, public domain. These primary State Department records document the Prague Spring uprising and the Soviet suppression, fitting W.62's focus on national uprisings against the Soviet Union and why they failed.</t>
+        </is>
+      </c>
+      <c r="S133" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12968,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -13073,7 +13061,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -13166,7 +13154,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -13263,7 +13251,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -13356,7 +13344,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -13453,7 +13441,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -13546,7 +13534,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -13643,7 +13631,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -13681,42 +13669,40 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Partition of India refugee migration, 1947</t>
+          <t>U.S. newspaper front-page coverage of the Partition of India and Pakistan, August 1947</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>newspaper</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>press photographers</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
+          <t>Contemporary U.S. newspaper press (various)</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>1947</v>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>Chronicling America, Library of Congress (loc.gov/chroniclingamerica)</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (pre-1963 U.S. newspaper, no copyright renewal)</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Partition+India+Pakistan+1947+refugees</t>
+          <t>https://www.loc.gov/collections/chronicling-america/?q=India+Pakistan+partition+1947</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
@@ -13726,32 +13712,32 @@
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>The Partition of India, 1947. Library of Congress.</t>
+          <t>"India Partitioned; Pakistan Born" and related coverage, U.S. newspapers, August 1947, via Chronicling America, Library of Congress.</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>Photograph of mass refugee migration during the 1947 Partition.</t>
+          <t>August 1947 U.S. newspaper front pages reporting the partition of British India into India and Pakistan and the resulting mass refugee migration.</t>
         </is>
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05</t>
+          <t>SSP.01; SSP.02; SSP.03</t>
         </is>
       </c>
       <c r="R142" s="2" t="inlineStr">
         <is>
-          <t>Rights caution: 1947 press photos may still be under copyright — verify.</t>
-        </is>
-      </c>
-      <c r="S142" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>Pre-1963 U.S. newspapers in Chronicling America are public domain. Contemporary 1947 reporting on Partition and the refugee crisis fits W.67's causes-and-effects focus, replacing a copyrighted press photo with PD newspaper text.</t>
+        </is>
+      </c>
+      <c r="S142" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -13833,7 +13819,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -13871,42 +13857,40 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Gandhi and the Salt March, 1930</t>
+          <t>U.S. newspaper coverage of Gandhi's Salt March and civil disobedience campaign, 1930</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>newspaper</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>press photographers</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
+          <t>Contemporary U.S. newspaper press (various)</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>1930</v>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>Chronicling America, Library of Congress (loc.gov/chroniclingamerica)</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (pre-1929/pre-1963 U.S. newspaper, no copyright renewal)</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Gandhi+Salt+March+1930</t>
+          <t>https://www.loc.gov/collections/chronicling-america/?q=Gandhi+salt+march+1930</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -13916,17 +13900,17 @@
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>Mohandas Gandhi and the Salt March, 1930. Library of Congress.</t>
+          <t>Coverage of Mohandas Gandhi's Salt March, U.S. newspapers, 1930, via Chronicling America, Library of Congress.</t>
         </is>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>Photograph of Gandhi leading the 1930 Salt March.</t>
+          <t>1930 U.S. newspaper articles reporting Mohandas Gandhi's Salt March and nonviolent civil disobedience against British salt taxes in India.</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -13936,12 +13920,12 @@
       </c>
       <c r="R144" s="2" t="inlineStr">
         <is>
-          <t>Rights caution: verify individual photo; some 1930 press images remain under copyright.</t>
-        </is>
-      </c>
-      <c r="S144" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>Pre-1963 U.S. newspapers in Chronicling America are public domain. This contemporaneous reporting on Gandhi's nonviolent resistance supports W.68's focus on Gandhi's role, replacing a copyrighted Salt March photograph.</t>
+        </is>
+      </c>
+      <c r="S144" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -13968,42 +13952,40 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru and Indian independence, 1947</t>
+          <t>U.S. newspaper coverage of Indian independence and Nehru's new government, August 1947</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>newspaper</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>press/official photographers</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
+          <t>Contemporary U.S. newspaper press (various)</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>1947</v>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>Chronicling America, Library of Congress (loc.gov/chroniclingamerica)</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (pre-1963 U.S. newspaper, no copyright renewal)</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Nehru+Indian+independence+1947</t>
+          <t>https://www.loc.gov/collections/chronicling-america/?q=India+independence+Nehru+1947</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
@@ -14013,32 +13995,32 @@
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru at Indian independence, 1947. Library of Congress.</t>
+          <t>Coverage of Indian independence and Prime Minister Jawaharlal Nehru, U.S. newspapers, August 1947, via Chronicling America, Library of Congress.</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>Photograph of Nehru marking India's 1947 independence.</t>
+          <t>August 1947 U.S. newspaper reports on India gaining independence and Jawaharlal Nehru becoming its first prime minister.</t>
         </is>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R145" s="2" t="inlineStr">
         <is>
-          <t>Verify individual item rights.</t>
-        </is>
-      </c>
-      <c r="S145" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>Pre-1963 U.S. newspapers in Chronicling America are public domain. Contemporaneous 1947 reporting on Nehru and Indian independence fits W.68's focus on the leaders who built India's democratic government, replacing a copyrighted press photo.</t>
+        </is>
+      </c>
+      <c r="S145" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -14065,42 +14047,40 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>African independence leaders (Nkrumah, Kenyatta, Lumumba)</t>
+          <t>Foreign Relations of the United States, 1958-1960, Volume XIV, Africa</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>press/official photographers</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>1950s-1960s</t>
-        </is>
+          <t>U.S. Department of State, Office of the Historian</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>1960</v>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>Office of the Historian, U.S. Department of State (history.state.gov)</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=African+independence+leaders+Nkrumah+Kenyatta</t>
+          <t>https://history.state.gov/historicaldocuments/search?q=Africa+independence+1958-1960</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
@@ -14110,32 +14090,32 @@
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>African independence leaders, 1950s-60s. Library of Congress.</t>
+          <t>Foreign Relations of the United States, 1958-1960, Vol. XIV, Africa (Washington, D.C.: U.S. Government Printing Office), documents on African decolonization and nationalist leaders.</t>
         </is>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>Photograph of African nationalist leaders at independence.</t>
+          <t>U.S. State Department records from the late 1950s documenting African independence movements and nationalist leaders such as Nkrumah, Kenyatta, and Lumumba.</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R146" s="2" t="inlineStr">
         <is>
-          <t>Rights caution: mid-century press photos may still be under copyright — verify.</t>
-        </is>
-      </c>
-      <c r="S146" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>FRUS is a public-domain U.S. government publication. These diplomatic records document the goals and outcomes of African nationalist movements and their leaders, fitting W.69 without any copyrighted portrait photography.</t>
+        </is>
+      </c>
+      <c r="S146" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14197,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -14255,42 +14235,40 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Apartheid "petty apartheid" segregation signage</t>
+          <t>CIA map: South Africa — Black Homelands (Bantustans)</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>map</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>press/UN photographers</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>1950s-1980s</t>
-        </is>
+          <t>U.S. Central Intelligence Agency</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>1980</v>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>United Nations (hosted via *.edu archive)</t>
+          <t>Library of Congress / U.S. National Archives (loc.gov, archives.gov)</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=apartheid+South+Africa+segregation+sign</t>
+          <t>https://www.loc.gov/search/?q=CIA+map+South+Africa+homelands+bantustan</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
@@ -14300,32 +14278,32 @@
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>Apartheid segregation signage, South Africa. Library of Congress.</t>
+          <t>U.S. Central Intelligence Agency, map of South Africa's Black Homelands (Bantustans), via Library of Congress Geography and Map Division.</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>Photograph of "whites only" apartheid segregation signs.</t>
+          <t>U.S. government map showing the fragmented Black 'homelands' (Bantustans) created by South Africa's apartheid system of territorial segregation.</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02</t>
+          <t>SSP.01; SSP.06</t>
         </is>
       </c>
       <c r="R148" s="2" t="inlineStr">
         <is>
-          <t>Rights caution: verify individual photo before commercial use.</t>
-        </is>
-      </c>
-      <c r="S148" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>CIA/U.S. government maps are public domain. This map visualizes the spatial machinery of apartheid segregation (the Bantustan system) and supports W.70's geographic strand, replacing copyrighted apartheid-signage photography.</t>
+        </is>
+      </c>
+      <c r="S148" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -14352,42 +14330,40 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Anti-apartheid movement and Nelson Mandela</t>
+          <t>Comprehensive Anti-Apartheid Act of 1986 (Public Law 99-440)</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>public law / statute</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>press photographers</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>1980s-1990s</t>
-        </is>
+          <t>U.S. Congress</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>1986</v>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>U.S. Government Publishing Office (govinfo.gov)</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=anti-apartheid+Nelson+Mandela+protest</t>
+          <t>https://www.govinfo.gov/app/search/%7B%22query%22%3A%22Comprehensive%20Anti-Apartheid%20Act%201986%22%7D</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
@@ -14397,32 +14373,32 @@
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>The anti-apartheid movement and Nelson Mandela. Library of Congress.</t>
+          <t>Comprehensive Anti-Apartheid Act of 1986, Pub. L. No. 99-440, 100 Stat. 1086 (1986).</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Photograph of anti-apartheid protest or Mandela's release.</t>
+          <t>Text of the 1986 U.S. Comprehensive Anti-Apartheid Act imposing sanctions on South Africa and calling for the release of Nelson Mandela and other political prisoners.</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R149" s="2" t="inlineStr">
         <is>
-          <t>Rights caution: most Mandela-era photos are under copyright — verify.</t>
-        </is>
-      </c>
-      <c r="S149" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>U.S. public laws are public domain. This statute is a primary document of the international pressure that dismantled apartheid; it explicitly demands Mandela's release and legitimizes the ANC's cause, fitting W.70 without a copyrighted Mandela photograph.</t>
+        </is>
+      </c>
+      <c r="S149" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -14449,77 +14425,75 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Congo Crisis and post-independence conflict</t>
+          <t>Foreign Relations of the United States, 1961-1963, Volume XX, Congo Crisis</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>press/UN photographers</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>1960s</t>
-        </is>
+          <t>U.S. Department of State, Office of the Historian</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>1963</v>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Archives (NARA)</t>
+          <t>Office of the Historian, U.S. Department of State (history.state.gov)</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=Congo+Crisis+1960+independence+conflict</t>
+          <t>https://history.state.gov/historicaldocuments/frus1961-63v20</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>canonical</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>Post-independence conflict in Africa (Congo Crisis). U.S. National Archives.</t>
+          <t>Foreign Relations of the United States, 1961-1963, Vol. XX, Congo Crisis (Washington, D.C.: U.S. Government Printing Office).</t>
         </is>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>Photograph of conflict in newly independent Congo.</t>
+          <t>U.S. State Department records documenting the post-independence Congo Crisis, including political instability, secession, and foreign intervention.</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R150" s="2" t="inlineStr">
         <is>
-          <t>Rights caution: verify individual item.</t>
-        </is>
-      </c>
-      <c r="S150" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>FRUS is a public-domain U.S. government publication with a stable canonical URL (frus1961-63v20). The Congo Crisis volume documents the civil war, foreign intervention, and instability of a newly independent African state, directly fitting W.71.</t>
+        </is>
+      </c>
+      <c r="S150" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14575,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -14639,42 +14613,40 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>The Cuban Revolution and Fidel Castro, 1959</t>
+          <t>U.S. newspaper front-page coverage of the Cuban Revolution and Castro's takeover, January 1959</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>newspaper</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>press/U.S. government</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
+          <t>Contemporary U.S. newspaper press (various)</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>1959</v>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>Chronicling America, Library of Congress (loc.gov/chroniclingamerica)</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (pre-1963 U.S. newspaper, no copyright renewal)</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Cuban+Revolution+1959+Castro</t>
+          <t>https://www.loc.gov/collections/chronicling-america/?q=Castro+Cuba+revolution+1959</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
@@ -14684,32 +14656,32 @@
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>The Cuban Revolution, 1959. Library of Congress.</t>
+          <t>"Castro Takes Power in Cuba" and related coverage, U.S. newspapers, January 1959, via Chronicling America, Library of Congress.</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>Photograph of Fidel Castro and the 1959 Cuban Revolution.</t>
+          <t>January 1959 U.S. newspaper front pages reporting Fidel Castro's victory and the fall of the Batista regime in the Cuban Revolution.</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05</t>
+          <t>SSP.01; SSP.02; SSP.03</t>
         </is>
       </c>
       <c r="R152" s="2" t="inlineStr">
         <is>
-          <t>Rights caution: verify individual photo.</t>
-        </is>
-      </c>
-      <c r="S152" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>Pre-1963 U.S. newspapers in Chronicling America are public domain. Contemporaneous 1959 front-page coverage of Castro's revolution fits W.72's focus on ideological conflict and revolution in Latin America (Cuba), replacing a copyrighted Castro press photo.</t>
+        </is>
+      </c>
+      <c r="S152" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -14791,7 +14763,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -14884,7 +14856,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -14981,7 +14953,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -15019,42 +14991,40 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Cambodian genocide / Khmer Rouge (Tuol Sleng)</t>
+          <t>CIA research report: Kampuchea — A Demographic Catastrophe</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government report</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>press/documentary</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>1975-1979</t>
-        </is>
+          <t>U.S. Central Intelligence Agency</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>1980</v>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Archives (NARA)</t>
+          <t>CIA FOIA Electronic Reading Room / U.S. National Archives (cia.gov, archives.gov)</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=Cambodia+Khmer+Rouge+genocide+1975</t>
+          <t>https://www.cia.gov/readingroom/search/site/Kampuchea%20demographic%20catastrophe</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -15064,32 +15034,32 @@
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>The Cambodian genocide under the Khmer Rouge. U.S. National Archives.</t>
+          <t>U.S. Central Intelligence Agency, National Foreign Assessment Center, Kampuchea: A Demographic Catastrophe (1980).</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>Photograph documenting the Khmer Rouge genocide in Cambodia.</t>
+          <t>Declassified 1980 CIA report analyzing the massive population losses in Cambodia (Kampuchea) under Khmer Rouge rule.</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05</t>
+          <t>SSP.01; SSP.02; SSP.03</t>
         </is>
       </c>
       <c r="R156" s="2" t="inlineStr">
         <is>
-          <t>Sensitive/rights caution: verify individual item before use.</t>
-        </is>
-      </c>
-      <c r="S156" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>Declassified CIA reports are public domain U.S. government works. This report documents the demographic scale of the Cambodian genocide, fitting W.74's comparative genocide focus while avoiding the copyrighted Tuol Sleng photographs (whose reproduction rights are also ethically contested).</t>
+        </is>
+      </c>
+      <c r="S156" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -15116,42 +15086,40 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Rwandan genocide, 1994</t>
+          <t>Declassified U.S. State Department records on the 1994 Rwandan genocide</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Photograph / document</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>UN / U.S. government</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
+          <t>U.S. Department of State</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>1994</v>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Archives (NARA)</t>
+          <t>U.S. National Archives (archives.gov)</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=Rwanda+genocide+1994</t>
+          <t>https://catalog.archives.gov/search?q=Rwanda%20genocide%201994%20State%20Department</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
@@ -15161,32 +15129,32 @@
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>The Rwandan genocide, 1994. U.S. National Archives.</t>
+          <t>Declassified U.S. Department of State cables and memoranda on the Rwandan genocide, 1994, U.S. National Archives.</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>Photograph/document relating to the 1994 Rwandan genocide.</t>
+          <t>Declassified 1994 U.S. State Department cables reporting on the mass killings during the Rwandan genocide.</t>
         </is>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R157" s="2" t="inlineStr">
         <is>
-          <t>Sensitive/rights caution: verify individual item before use.</t>
-        </is>
-      </c>
-      <c r="S157" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>Declassified U.S. State Department records are public domain government works. These contemporaneous cables document the unfolding Rwandan genocide and the international response, fitting W.74 without a copyrighted press photograph. (If a cleaner canonical item is preferred, UN Security Council Resolution 955 (1994) creating the ICTR is an alternative, but UN documents carry usage terms rather than full public domain.)</t>
+        </is>
+      </c>
+      <c r="S157" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -15268,7 +15236,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -15365,7 +15333,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -15458,7 +15426,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -15551,7 +15519,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -15644,7 +15612,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -15737,7 +15705,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -15775,77 +15743,75 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>China's one-child policy</t>
+          <t>U.S. Census Bureau International Data Base: China population pyramids and demographic data</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Photograph / poster</t>
+          <t>data set / chart</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>press / Chinese sources</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>1979-2015</t>
-        </is>
+          <t>U.S. Census Bureau</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>2020</v>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>U.S. Census Bureau, International Programs (census.gov)</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=China+one+child+policy+poster</t>
+          <t>https://www.census.gov/data-tools/demo/idb/#/country?COUNTRY_YEAR=2020&amp;COUNTRY_YR_ANIM=2020&amp;menu=popViz&amp;FIPS_SINGLE=CH</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>canonical</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>China's one-child policy. Library of Congress.</t>
+          <t>U.S. Census Bureau, International Data Base, population pyramids and age-structure data for China (accessed via census.gov).</t>
         </is>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>Photograph/poster illustrating China's one-child population policy.</t>
+          <t>U.S. Census Bureau population pyramid for China showing the age-structure distortions produced by decades of the one-child policy.</t>
         </is>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02</t>
+          <t>SSP.01; SSP.03; SSP.06</t>
         </is>
       </c>
       <c r="R164" s="2" t="inlineStr">
         <is>
-          <t>Rights caution: contemporary/PRC materials may be under copyright — verify.</t>
-        </is>
-      </c>
-      <c r="S164" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>U.S. Census Bureau data and generated population pyramids are public domain. A demographic data chart visualizes the effects of China's one-child policy on age structure and sex ratio, fitting W.78's focus on population policy far better (and more safely) than a copyrighted policy poster or press photo.</t>
+        </is>
+      </c>
+      <c r="S164" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -15927,7 +15893,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -16020,7 +15986,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -16113,7 +16079,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -16206,7 +16172,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -16299,7 +16265,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -16392,7 +16358,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -16489,7 +16455,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -16586,7 +16552,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -16679,7 +16645,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -16776,7 +16742,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -16869,7 +16835,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -16962,7 +16928,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -17055,7 +17021,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -17152,7 +17118,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -17249,7 +17215,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -17342,7 +17308,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -17439,7 +17405,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -17532,7 +17498,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -17625,7 +17591,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -17722,7 +17688,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -17760,42 +17726,40 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>The Iranian Revolution, 1979</t>
+          <t>Foreign Relations of the United States, 1977-1980, Iran (Revolution) volume</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>press photographers</t>
-        </is>
-      </c>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
+          <t>U.S. Department of State, Office of the Historian</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="n">
+        <v>1979</v>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>Office of the Historian, U.S. Department of State (history.state.gov)</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>Rights vary by item — verify PD/commercial status at repository</t>
+          <t>Public domain (U.S. federal government work)</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Iranian+Revolution+1979+Khomeini</t>
+          <t>https://history.state.gov/historicaldocuments/search?q=Iran+revolution+1977-1980</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
@@ -17805,32 +17769,32 @@
       </c>
       <c r="N185" s="2" t="inlineStr">
         <is>
-          <t>The Iranian Revolution, 1979. Library of Congress.</t>
+          <t>Foreign Relations of the United States, 1977-1980, Iran (Washington, D.C.: U.S. Government Printing Office), documents on the 1978-1979 Iranian Revolution.</t>
         </is>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
-          <t>Photograph of the 1979 Iranian Revolution.</t>
+          <t>U.S. State Department records from 1978-1979 documenting the Iranian Revolution and the fall of the Shah amid a rising religious-political movement.</t>
         </is>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R185" s="2" t="inlineStr">
         <is>
-          <t>Rights caution: contemporary press photos may be under copyright — verify.</t>
-        </is>
-      </c>
-      <c r="S185" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: confirm commercial license</t>
+          <t>FRUS is a public-domain U.S. government publication. These diplomatic records document the ideology and popular religious movement of the 1979 Iranian Revolution, fitting W.88's focus on governing ideologies and religious/democratic movements in the Middle East, replacing a copyrighted revolution photograph.</t>
+        </is>
+      </c>
+      <c r="S185" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -17912,7 +17876,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -18009,7 +17973,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">

--- a/crosswalk/xlsx/hs-world-history__primary-source-crosswalk.xlsx
+++ b/crosswalk/xlsx/hs-world-history__primary-source-crosswalk.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — published c. 1701 (pre-1929)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Rigaud state portrait embodies divine-right absolutism; confirm CC0 open-access item.</t>
+          <t>Rigaud state portrait embodies divine-right absolutism; published c. 1701, well pre-1929.</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — official document text (Magna Carta, 1215)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — official document text (1689)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — medieval manuscript, pre-1929</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — published c. 1650s (pre-1929)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — official document text (1789)</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — published early 19th c. (pre-1929)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — official document text (1789)</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — official document text (1804)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — published pre-1929</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — published pre-1929 (19th c.)</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3608,7 +3608,11 @@
           <t>SSP.01; SSP.02</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Use a pre-1929 19th-century engraving/illustration of the locomotive.</t>
+        </is>
+      </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5029,32 +5033,32 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Battle of Adwa (Adowa), 1896</t>
+          <t>The Battle of Adwa, 1896 (contemporary illustrated press engraving)</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Painting/print</t>
+          <t>Print/engraving</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Ethiopian traditional artists</t>
+          <t>contemporary European illustrated press</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>c. 1896-1920s</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Smithsonian National Museum of African Art</t>
+          <t>Library of Congress</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — published pre-1929</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -5064,7 +5068,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=Battle+of+Adwa+Ethiopia+painting</t>
+          <t>https://www.loc.gov/search/?q=Battle+of+Adwa+Adowa+1896+Ethiopia+Italy</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -5074,12 +5078,12 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Depiction of the Battle of Adwa, 1896. Smithsonian National Museum of African Art.</t>
+          <t>The Battle of Adwa (Ethiopian victory over Italy), illustrated press engraving, 1896. Library of Congress.</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Ethiopian painting of the victory over Italian forces at Adwa.</t>
+          <t>1896 engraving depicting the Ethiopian victory over Italian forces at the Battle of Adwa.</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -5094,7 +5098,7 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>Confirm PD/open-access status of the specific Ethiopian painting.</t>
+          <t>Replaces an Ethiopian painting of uncertain (possibly post-1929) date with a guaranteed-PD pre-1929 press engraving of the same battle, still illustrating Ethiopia's successful resistance for W.22.</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -5806,7 +5810,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — published c. 1854 (pre-1929)</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -5899,7 +5903,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — published 1894-1895 (pre-1929)</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -7201,7 +7205,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — treaty text (1918)</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -7241,7 +7245,7 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>Marked search: confirm exact Avalon path for Brest-Litovsk menu.</t>
+          <t>Treaty text hosted on the Avalon Project subject menu for Brest-Litovsk.</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
@@ -7670,7 +7674,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — treaty text (1919)</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -7856,7 +7860,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work (1918)</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -7896,7 +7900,7 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>Contrasts stated goals with Versailles outcome.</t>
+          <t>Contrasts stated goals with Versailles outcome; a U.S. government work and pre-1929.</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr">
@@ -8046,7 +8050,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — treaty text (League Covenant, 1919)</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -8232,7 +8236,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — published 1918-1921 (pre-1929)</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -8272,7 +8276,7 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>Confirm PD status of the specific poster (most pre-1929 Soviet works are PD).</t>
+          <t>Bounded to 1918-1921, so guaranteed public domain under the pre-1929 rule (applies to works published anywhere).</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr">
@@ -8389,32 +8393,32 @@
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>1920s modern design and Art Deco</t>
+          <t>1920s American consumer-culture photographs (National Photo Company Collection)</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Design/print</t>
+          <t>Photograph</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>1920s designers</t>
+          <t>National Photo Company</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>1920s</t>
+          <t>c. 1920-1928</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>The Metropolitan Museum of Art</t>
+          <t>Library of Congress</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — published pre-1929</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -8424,7 +8428,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>https://www.metmuseum.org/search-results?q=Art+Deco+1920s+design</t>
+          <t>https://www.loc.gov/search/?q=National+Photo+Company+1920s+automobile+radio</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -8434,12 +8438,12 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Art Deco design, 1920s. The Metropolitan Museum of Art.</t>
+          <t>1920s consumer-culture photographs, National Photo Company Collection, c.1920-1928. Library of Congress.</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Example of 1920s Art Deco design.</t>
+          <t>1920s photographs of automobiles, radios, and consumer culture illustrating Jazz Age trends.</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -8454,7 +8458,7 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>Verify open-access/PD status of the specific object.</t>
+          <t>Replaces a Met Art Deco design object of uncertain (possibly post-1928) date with guaranteed-PD pre-1929 LoC photographs of 1920s cultural and economic trends for W.39.</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr">
@@ -8765,32 +8769,30 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Rise of the Nazi Party / early rallies</t>
+          <t>Foreign Relations of the United States, 1933 — documents on Germany and the Nazi seizure of power</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>official/press photographers</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>1920s-1933</t>
-        </is>
+          <t>U.S. Department of State, Office of the Historian</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>1933</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Archives (NARA)</t>
+          <t>Office of the Historian, U.S. Department of State (history.state.gov)</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -8800,7 +8802,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=Nazi+Party+rally+1920s+rise+Hitler</t>
+          <t>https://history.state.gov/historicaldocuments/search?q=Germany+1933+Hitler+Nazi</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -8810,12 +8812,12 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Rise of the Nazi Party. U.S. National Archives.</t>
+          <t>Foreign Relations of the United States, 1933, documents on Germany and the Nazi consolidation of power (Washington, D.C.: U.S. Government Printing Office).</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Photograph of an early Nazi Party rally in Germany.</t>
+          <t>U.S. State Department diplomatic records from 1933 documenting Hitler's rise and the Nazi consolidation of power amid economic and political instability.</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -8830,7 +8832,7 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>Verify rights of individual images (many are captured German records, PD).</t>
+          <t>Replaces German-origin Nazi-rally photographs (copyright not guaranteed) with a public-domain U.S. government FRUS volume documenting the instability that produced the Nazi regime, fitting W.41.</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -8862,7 +8864,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Totalitarian propaganda posters (Nazi, Fascist, Soviet)</t>
+          <t>U.S. Office of War Information anti-Axis propaganda poster (Hitler, Mussolini, Tojo)</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -8872,12 +8874,12 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>state artists</t>
+          <t>U.S. Office of War Information</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>1920s-1940s</t>
+          <t>1942-1945</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -8887,7 +8889,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -8897,7 +8899,7 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=propaganda+poster+Nazi+fascist+Soviet</t>
+          <t>https://catalog.archives.gov/search?q=Office+of+War+Information+poster+Hitler+Mussolini+Tojo</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -8907,12 +8909,12 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Totalitarian propaganda posters. U.S. National Archives.</t>
+          <t>U.S. Office of War Information anti-Axis propaganda poster, 1942-1945. U.S. National Archives.</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Propaganda posters glorifying totalitarian leaders.</t>
+          <t>U.S. wartime poster caricaturing the Axis totalitarian leaders Hitler, Mussolini, and Tojo.</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -8927,7 +8929,7 @@
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>Compare three regimes; verify item rights (captured records often PD).</t>
+          <t>Replaces foreign Nazi/Fascist/Soviet posters (copyright not guaranteed) with a public-domain U.S. government (OWI) poster depicting the totalitarian leaders for the W.42 comparison.</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr">
@@ -8959,32 +8961,32 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Photographs of Hitler, Mussolini, and Stalin</t>
+          <t>Foreign Relations of the United States — diplomatic records on Nazi Germany, Fascist Italy, and the Soviet Union (1930s)</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>official/press photographers</t>
+          <t>U.S. Department of State, Office of the Historian</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>1930s-1940s</t>
+          <t>1930s</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>Office of the Historian, U.S. Department of State (history.state.gov)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -8994,7 +8996,7 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Hitler+Mussolini+Stalin+dictators</t>
+          <t>https://history.state.gov/historicaldocuments/search?q=Germany+Italy+Soviet+Union+1930s</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -9004,12 +9006,12 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Photographs of Hitler, Mussolini, and Stalin. Library of Congress.</t>
+          <t>Foreign Relations of the United States, 1930s volumes on Germany, Italy, and the Soviet Union. Office of the Historian, U.S. Dept. of State.</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Portrait photographs of the three dictators.</t>
+          <t>U.S. State Department records from the 1930s describing the goals and characteristics of the Hitler, Mussolini, and Stalin regimes.</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -9024,7 +9026,7 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>Verify individual item rights.</t>
+          <t>Replaces foreign-origin portrait photographs of the three dictators with public-domain U.S. government FRUS records that document their regimes for the W.42 comparison.</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr">
@@ -9149,22 +9151,22 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Greater East Asia Co-Prosperity Sphere map/poster</t>
+          <t>U.S. government map of Japanese expansion and resource areas in the Pacific, 1941-1942</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Map/poster</t>
+          <t>Map</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Japanese government</t>
+          <t>U.S. Army Map Service / Office of Strategic Services</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>c. 1940-1942</t>
+          <t>1941-1942</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -9174,7 +9176,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -9184,7 +9186,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=Greater+East+Asia+Co-Prosperity+Sphere+Japan</t>
+          <t>https://catalog.archives.gov/search?q=map+Japanese+expansion+Pacific+resources+1942</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -9194,12 +9196,12 @@
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Greater East Asia Co-Prosperity Sphere. U.S. National Archives.</t>
+          <t>U.S. government map of Japanese territorial expansion and resource zones in the Pacific, 1941-1942. U.S. National Archives.</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Japanese map/poster of the Greater East Asia Co-Prosperity Sphere.</t>
+          <t>U.S. wartime map showing Japanese expansion and the oil, rubber, and mineral resources driving Pacific tensions.</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -9214,7 +9216,7 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>Verify rights (captured Japanese records generally PD).</t>
+          <t>Replaces a Japanese-government Co-Prosperity Sphere map/poster (copyright not guaranteed) with a public-domain U.S. government map of Japanese expansion and resources, fitting W.43's geography/resources focus.</t>
         </is>
       </c>
       <c r="S94" s="3" t="inlineStr">
@@ -9343,32 +9345,30 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Second Sino-Japanese War, 1937 (invasion of China)</t>
+          <t>Foreign Relations of the United States, Japan: 1931-1941 (Japanese aggression in China)</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>press/official photographers</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>1937-1938</t>
-        </is>
+          <t>U.S. Department of State</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>1943</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Archives (NARA)</t>
+          <t>Office of the Historian, U.S. Department of State (history.state.gov)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=Second+Sino-Japanese+War+1937+China</t>
+          <t>https://history.state.gov/historicaldocuments/search?q=Japan+1931-1941+China+aggression</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Second Sino-Japanese War, 1937. U.S. National Archives.</t>
+          <t>Foreign Relations of the United States, Japan, 1931-1941 (Washington, D.C.: U.S. Government Printing Office, 1943), documents on Japanese aggression in China.</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Photograph of the Japanese invasion of China in 1937.</t>
+          <t>U.S. State Department records documenting Japan's 1937 invasion of China and atrocities such as the Nanjing Massacre.</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -9406,7 +9406,11 @@
           <t>SSP.01; SSP.02; SSP.05</t>
         </is>
       </c>
-      <c r="R96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>Replaces a 1937 press/official photograph (copyright not guaranteed) with the public-domain FRUS Japan volumes documenting Japanese aggression and atrocities in China, fitting W.44.</t>
+        </is>
+      </c>
       <c r="S96" s="3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9461,7 +9465,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — official agreement text (1938)</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -9476,7 +9480,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>canonical</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -9501,7 +9505,7 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>Marked search: confirm exact Avalon path.</t>
+          <t>Official agreement text hosted on the Avalon Project.</t>
         </is>
       </c>
       <c r="S97" s="3" t="inlineStr">
@@ -9533,32 +9537,32 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>American isolationism / "America First" (1930s)</t>
+          <t>The U.S. Neutrality Acts of 1935-1939 (statute text)</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Poster/cartoon/photograph</t>
+          <t>public law / statute</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>1930s sources</t>
+          <t>U.S. Congress</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>1935-1941</t>
+          <t>1935-1939</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>U.S. Government Publishing Office (govinfo.gov)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work (federal statute text)</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -9568,7 +9572,7 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=America+First+isolationism+1940+neutrality</t>
+          <t>https://www.govinfo.gov/app/search/%7B%22query%22%3A%22Neutrality%20Act%201935%201937%201939%22%7D</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -9578,12 +9582,12 @@
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>American isolationism, late 1930s. Library of Congress.</t>
+          <t>Neutrality Acts of 1935, 1937, and 1939, U.S. Statutes at Large. U.S. Government Publishing Office.</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Isolationist "America First" imagery before U.S. entry into WWII.</t>
+          <t>Text of the U.S. Neutrality Acts of the 1930s embodying American isolationism before World War II.</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -9598,7 +9602,7 @@
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>Verify individual item rights.</t>
+          <t>Replaces mixed 1935-1941 isolationist posters/cartoons/photos (copyright not guaranteed) with the public-domain text of the Neutrality Acts, a primary document of U.S. isolationism for W.45.</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr">
@@ -10091,7 +10095,7 @@
       <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Portraits/photographs of WWII leaders</t>
+          <t>U.S. Army Signal Corps photographs of Allied wartime leaders</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -10101,22 +10105,22 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>official/press photographers</t>
+          <t>U.S. Army Signal Corps</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>1939-1945</t>
+          <t>1941-1945</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>U.S. National Archives (NARA)</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -10126,7 +10130,7 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=World+War+II+leaders+Churchill+Roosevelt+Truman+Tojo</t>
+          <t>https://catalog.archives.gov/search?q=Signal+Corps+Roosevelt+Churchill+Truman+Stalin+conference</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -10136,12 +10140,12 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>World War II leaders. Library of Congress.</t>
+          <t>U.S. Army Signal Corps photographs of Allied leaders at wartime conferences, 1941-1945. U.S. National Archives.</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Portrait photographs of the major World War II leaders.</t>
+          <t>U.S. government photographs of Roosevelt, Churchill, Truman, and Stalin at World War II conferences.</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -10156,7 +10160,7 @@
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>Verify individual item rights.</t>
+          <t>Replaces a mixed LoC set of leader photographs (some foreign/press, copyright not guaranteed) with public-domain U.S. Army Signal Corps photographs of the Allied leaders for W.48.</t>
         </is>
       </c>
       <c r="S104" s="3" t="inlineStr">
@@ -10188,32 +10192,30 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Nazi anti-Jewish boycott and Kristallnacht, 1933-1938</t>
+          <t>Foreign Relations of the United States, 1938 — the Evian Conference and Jewish refugees</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>official/press photographers</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>1933-1938</t>
-        </is>
+          <t>U.S. Department of State</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>1938</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Archives (NARA)</t>
+          <t>Office of the Historian, U.S. Department of State (history.state.gov)</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -10223,7 +10225,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=Nazi+anti-Jewish+boycott+Kristallnacht+1938</t>
+          <t>https://history.state.gov/historicaldocuments/search?q=Evian+Conference+1938+refugees</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -10233,12 +10235,12 @@
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>Nazi persecution of Jews, 1933-1938. U.S. National Archives.</t>
+          <t>Foreign Relations of the United States, 1938, documents on the Evian Conference and the Jewish refugee crisis. Office of the Historian, U.S. Dept. of State.</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>Photograph of the 1933 anti-Jewish boycott or 1938 Kristallnacht damage.</t>
+          <t>U.S. State Department records from 1938 on the Evian Conference and the international failure to admit Jewish refugees fleeing Nazi persecution.</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -10253,7 +10255,7 @@
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>Verify item rights (captured German records generally PD).</t>
+          <t>Replaces Kristallnacht/boycott photographs (copyright not guaranteed) with public-domain FRUS records on the Evian Conference, directly supporting W.49's focus on why many Jews were unable to leave.</t>
         </is>
       </c>
       <c r="S105" s="3" t="inlineStr">
@@ -10310,7 +10312,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — official statute text (Nuremberg Laws, 1935)</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -10348,7 +10350,11 @@
           <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
-      <c r="R106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>Statute text (government edict); the NARA-held record is a captured German government document.</t>
+        </is>
+      </c>
       <c r="S106" s="3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -10471,32 +10477,30 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Warsaw Ghetto and ghetto uprising, 1943</t>
+          <t>Nazi Conspiracy and Aggression (U.S. GPO, 1946) — documentary evidence of the Holocaust</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>official records</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>1940-1943</t>
-        </is>
+          <t>U.S. Office of Chief of Counsel for the Prosecution of Axis Criminality</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>1946</v>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Archives (NARA)</t>
+          <t>U.S. Government Publishing Office / Library of Congress</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -10506,7 +10510,7 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=Warsaw+Ghetto+uprising+1943</t>
+          <t>https://www.loc.gov/search/?q=Nazi+Conspiracy+and+Aggression+1946</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -10516,12 +10520,12 @@
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>The Warsaw Ghetto, 1943. U.S. National Archives.</t>
+          <t>Office of U.S. Chief of Counsel, Nazi Conspiracy and Aggression (Washington, D.C.: U.S. Government Printing Office, 1946).</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Photograph from the Warsaw Ghetto and 1943 uprising.</t>
+          <t>Documentary evidence compiled by U.S. prosecutors for the Nuremberg trials, including records of the Nazi extermination of the Jews.</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -10536,7 +10540,7 @@
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>Verify item rights (Stroop Report images are captured records, PD).</t>
+          <t>Replaces Warsaw Ghetto photographs (copyright/ethical status not guaranteed) with the public-domain U.S. GPO Nuremberg evidence volumes documenting the state-sponsored mass murder of the Jews for W.50.</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr">
@@ -10593,7 +10597,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — official document text (1941)</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -10686,7 +10690,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — official agreement text (Yalta Protocol, 1945)</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -11244,7 +11248,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work (1947)</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -11282,7 +11286,11 @@
           <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
-      <c r="R116" s="2" t="inlineStr"/>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>Delivered by the U.S. Secretary of State in his official capacity — a U.S. government work.</t>
+        </is>
+      </c>
       <c r="S116" s="3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11523,7 +11531,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — UN partition map (official document, 1947)</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -11561,7 +11569,11 @@
           <t>SSP.01; SSP.02; SSP.06</t>
         </is>
       </c>
-      <c r="R119" s="2" t="inlineStr"/>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>Use the official UN Resolution 181 partition map (also mirrored by the U.S. State Dept Office of the Historian).</t>
+        </is>
+      </c>
       <c r="S119" s="3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11591,32 +11603,30 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>"Sinews of Peace" (Iron Curtain speech), 1946</t>
+          <t>George F. Kennan, "Long Telegram" (1946)</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Speech (text)</t>
+          <t>government document (diplomatic cable)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Winston Churchill</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>1946</t>
-        </is>
+          <t>George F. Kennan, U.S. Department of State</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>1946</v>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>U.S. Dept. of State, Office of the Historian</t>
+          <t>U.S. National Archives / Office of the Historian, U.S. Department of State</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -11626,7 +11636,7 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>https://history.state.gov/search?q=Churchill+Iron+Curtain+1946+Sinews+of+Peace</t>
+          <t>https://history.state.gov/historicaldocuments/search?q=Kennan+long+telegram+1946</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
@@ -11636,12 +11646,12 @@
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>Winston Churchill, "Sinews of Peace" (Iron Curtain speech), 1946. Office of the Historian.</t>
+          <t>George F. Kennan, telegram from Moscow ("Long Telegram"), February 22, 1946. U.S. National Archives / Office of the Historian, U.S. Dept. of State.</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Text of Churchill's 1946 Iron Curtain speech.</t>
+          <t>Text of Kennan's 1946 Long Telegram analyzing postwar Soviet expansion and the shifting balance of power.</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
@@ -11656,7 +11666,7 @@
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>Verify best PD host; text widely reproduced by U.S. gov sources.</t>
+          <t>Replaces Churchill's copyrighted "Iron Curtain" speech with the public-domain U.S. government Long Telegram, which addresses the same postwar Soviet power shift for W.56.</t>
         </is>
       </c>
       <c r="S120" s="3" t="inlineStr">
@@ -11688,7 +11698,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Map of Cold War divided Europe / Iron Curtain</t>
+          <t>U.S. government (CIA) map of Cold War Europe and the Soviet bloc</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -11698,12 +11708,12 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>postwar cartographers</t>
+          <t>U.S. Central Intelligence Agency</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>c. 1946-1955</t>
+          <t>c. 1950</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -11713,7 +11723,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -11723,7 +11733,7 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Iron+Curtain+divided+Europe+map+Cold+War</t>
+          <t>https://www.loc.gov/search/?q=CIA+map+Europe+Soviet+bloc+iron+curtain</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
@@ -11733,12 +11743,12 @@
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>Map of Cold War Europe divided by the Iron Curtain. Library of Congress.</t>
+          <t>U.S. Central Intelligence Agency map of divided Cold War Europe. Library of Congress, Geography &amp; Map Division.</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Map showing the Iron Curtain dividing East and West Europe.</t>
+          <t>U.S. government map showing the Iron Curtain dividing Western Europe from the Soviet bloc.</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
@@ -11751,7 +11761,11 @@
           <t>SSP.01; SSP.02; SSP.06</t>
         </is>
       </c>
-      <c r="R121" s="2" t="inlineStr"/>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>Replaces an unattributed postwar map (PD not guaranteed) with a public-domain U.S. government (CIA) map of Cold War Europe for W.56.</t>
+        </is>
+      </c>
       <c r="S121" s="3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11781,32 +11795,32 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Founding of the People's Republic of China, 1949</t>
+          <t>U.S. government (CIA) map of the Communist advance in China, 1949-1950</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>Map</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>contemporary photographers</t>
+          <t>U.S. Central Intelligence Agency</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1949-1950</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>Library of Congress / U.S. National Archives</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -11816,7 +11830,7 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Mao+Zedong+founding+People%27s+Republic+China+1949</t>
+          <t>https://www.loc.gov/search/?q=CIA+map+communist+China+1949+1950</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
@@ -11826,12 +11840,12 @@
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>Founding of the People's Republic of China, 1949. Library of Congress.</t>
+          <t>U.S. Central Intelligence Agency map of the Chinese Communist takeover, 1949-1950. Library of Congress.</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Mao Zedong proclaiming the People's Republic of China in 1949.</t>
+          <t>U.S. government map showing the Communist consolidation of control over China around 1949-1950.</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
@@ -11841,12 +11855,12 @@
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02; SSP.05</t>
+          <t>SSP.01; SSP.02; SSP.06</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>Verify individual item rights.</t>
+          <t>Replaces a 1949 Chinese-origin photograph (copyright not guaranteed) with a public-domain U.S. government map of the Communist takeover, complementing the China White Paper for W.57.</t>
         </is>
       </c>
       <c r="S122" s="3" t="inlineStr">
@@ -11998,7 +12012,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work (1947)</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -12036,7 +12050,11 @@
           <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
-      <c r="R124" s="2" t="inlineStr"/>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>Presidential address delivered in official capacity — a U.S. government work.</t>
+        </is>
+      </c>
       <c r="S124" s="3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12066,32 +12084,30 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Early Cold War political cartoon / containment map</t>
+          <t>NSC-68: United States Objectives and Programs for National Security (1950)</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Cartoon / map</t>
+          <t>government document</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>late 1940s sources</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>1947-1950</t>
-        </is>
+          <t>U.S. National Security Council</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>1950</v>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>Office of the Historian, U.S. Department of State / U.S. National Archives</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -12101,22 +12117,22 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Cold+War+containment+cartoon+Soviet+Union</t>
+          <t>https://history.state.gov/historicaldocuments/frus1950v01</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>search</t>
+          <t>canonical</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>Early Cold War cartoon. Library of Congress.</t>
+          <t>NSC-68, "United States Objectives and Programs for National Security," April 14, 1950, in FRUS, 1950, Vol. I. Office of the Historian, U.S. Dept. of State.</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Cartoon depicting U.S.-Soviet Cold War rivalry.</t>
+          <t>Text of the 1950 NSC-68 policy paper defining U.S. Cold War containment strategy against the Soviet Union.</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
@@ -12126,12 +12142,12 @@
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>SSP.01; SSP.02</t>
+          <t>SSP.01; SSP.02; SSP.04</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>Verify item rights.</t>
+          <t>Replaces a post-1929 press cartoon (copyright not guaranteed) with the public-domain U.S. government NSC-68 policy paper, a core primary source on Cold War characteristics and U.S.-Soviet tensions for W.58.</t>
         </is>
       </c>
       <c r="S125" s="3" t="inlineStr">
@@ -12188,7 +12204,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — treaty text (1949)</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -12281,7 +12297,7 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — treaty text (1955)</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -12721,32 +12737,30 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Hungarian Uprising of 1956</t>
+          <t>Foreign Relations of the United States, 1955-1957, Eastern Europe (Hungarian Revolution)</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>press photographers</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
+          <t>U.S. Department of State, Office of the Historian</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>1957</v>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Archives (NARA)</t>
+          <t>Office of the Historian, U.S. Department of State (history.state.gov)</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -12756,7 +12770,7 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=Hungarian+Revolution+1956+uprising</t>
+          <t>https://history.state.gov/historicaldocuments/search?q=Hungary+1956+revolution</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
@@ -12766,12 +12780,12 @@
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>The Hungarian Uprising, 1956. U.S. National Archives.</t>
+          <t>Foreign Relations of the United States, 1955-1957, Eastern Europe (Washington, D.C.: U.S. Government Printing Office), documents on the 1956 Hungarian Revolution.</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>Photograph of protesters and tanks during the 1956 Hungarian Uprising.</t>
+          <t>U.S. State Department records documenting the 1956 Hungarian Uprising and its suppression by Soviet forces.</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
@@ -12786,7 +12800,7 @@
       </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
-          <t>Verify individual item rights.</t>
+          <t>Replaces 1956 press photographs (copyright not guaranteed) with the public-domain FRUS Eastern Europe volume documenting the Hungarian Uprising and why it failed, fitting W.62.</t>
         </is>
       </c>
       <c r="S132" s="3" t="inlineStr">
@@ -13099,32 +13113,30 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Fall of the Berlin Wall, 1989</t>
+          <t>Public Papers of the Presidents: George H. W. Bush, 1989 — statements on the fall of the Berlin Wall</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>U.S. government / press</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
+          <t>President George H. W. Bush / U.S. Government Publishing Office</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>1989</v>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Archives (NARA)</t>
+          <t>U.S. Government Publishing Office (govinfo.gov)</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -13134,7 +13146,7 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=fall+of+the+Berlin+Wall+1989</t>
+          <t>https://www.govinfo.gov/app/search/%7B%22query%22%3A%22Bush%201989%20Berlin%20Wall%20Eastern%20Europe%22%7D</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -13144,12 +13156,12 @@
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>Fall of the Berlin Wall, 1989. U.S. National Archives.</t>
+          <t>Public Papers of the Presidents of the United States: George H. W. Bush, 1989. U.S. Government Publishing Office.</t>
         </is>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>People atop and dismantling the Berlin Wall in 1989.</t>
+          <t>Presidential statements from 1989 on the fall of the Berlin Wall and the collapse of communist governments in Eastern Europe.</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
@@ -13164,7 +13176,7 @@
       </c>
       <c r="R136" s="2" t="inlineStr">
         <is>
-          <t>Verify individual item rights.</t>
+          <t>Replaces a 1989 press photograph of the Berlin Wall's fall (copyright not guaranteed) with public-domain U.S. presidential papers documenting the collapse of communism for W.64.</t>
         </is>
       </c>
       <c r="S136" s="3" t="inlineStr">
@@ -13289,32 +13301,30 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Dissolution of the Soviet Union, 1991</t>
+          <t>Public Papers of the Presidents: George H. W. Bush, 1991 — statements on the dissolution of the Soviet Union</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>U.S. government / press</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
+          <t>President George H. W. Bush / U.S. Government Publishing Office</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>1991</v>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Archives (NARA)</t>
+          <t>U.S. Government Publishing Office (govinfo.gov)</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -13324,7 +13334,7 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=dissolution+Soviet+Union+1991</t>
+          <t>https://www.govinfo.gov/app/search/%7B%22query%22%3A%22Bush%201991%20Soviet%20Union%20dissolution%22%7D</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
@@ -13334,12 +13344,12 @@
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>The dissolution of the Soviet Union, 1991. U.S. National Archives.</t>
+          <t>Public Papers of the Presidents of the United States: George H. W. Bush, 1991. U.S. Government Publishing Office.</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>Photograph from the 1991 collapse of the Soviet Union.</t>
+          <t>Presidential statements from December 1991 on the dissolution of the Soviet Union and its consequences.</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
@@ -13354,7 +13364,7 @@
       </c>
       <c r="R138" s="2" t="inlineStr">
         <is>
-          <t>Verify individual item rights.</t>
+          <t>Replaces a 1991 press photograph (copyright not guaranteed) with public-domain U.S. presidential papers on the Soviet collapse and its consequences for W.65.</t>
         </is>
       </c>
       <c r="S138" s="3" t="inlineStr">
@@ -13764,7 +13774,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Map of the partition of British India, 1947</t>
+          <t>U.S. government (CIA) map of the 1947 partition of British India</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -13774,12 +13784,12 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>1947 cartographers</t>
+          <t>U.S. Central Intelligence Agency</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>c. 1947-1950</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -13789,7 +13799,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -13799,7 +13809,7 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=India+Pakistan+partition+map+1947+Radcliffe</t>
+          <t>https://www.loc.gov/search/?q=CIA+map+India+Pakistan+partition+1947</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
@@ -13809,12 +13819,12 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>Map of the partition of British India, 1947. Library of Congress.</t>
+          <t>U.S. Central Intelligence Agency map of the partition of British India into India and Pakistan, 1947. Library of Congress.</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>Map showing the division of India into India and Pakistan.</t>
+          <t>U.S. government map showing the 1947 division of British India into India and Pakistan.</t>
         </is>
       </c>
       <c r="P143" s="2" t="inlineStr">
@@ -13827,7 +13837,11 @@
           <t>SSP.01; SSP.02; SSP.06</t>
         </is>
       </c>
-      <c r="R143" s="2" t="inlineStr"/>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>Replaces an unattributed 1947 map (PD not guaranteed) with a public-domain U.S. government (CIA) map of the Partition for W.67.</t>
+        </is>
+      </c>
       <c r="S143" s="3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14142,32 +14156,30 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Nasser and the nationalization of the Suez Canal, 1956</t>
+          <t>Foreign Relations of the United States, 1955-1957, Suez Crisis volumes (Nasser and the Suez Canal)</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>U.S. government / press</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
+          <t>U.S. Department of State, Office of the Historian</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>1957</v>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Archives (NARA)</t>
+          <t>Office of the Historian, U.S. Department of State (history.state.gov)</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -14177,7 +14189,7 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=Nasser+Suez+Canal+nationalization+1956</t>
+          <t>https://history.state.gov/historicaldocuments/search?q=Suez+crisis+1956+Nasser</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
@@ -14187,12 +14199,12 @@
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>Gamal Abdel Nasser and the Suez Crisis, 1956. U.S. National Archives.</t>
+          <t>Foreign Relations of the United States, 1955-1957, Suez Crisis volumes (Washington, D.C.: U.S. Government Printing Office), documents on Nasser's nationalization of the Suez Canal.</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>Photograph related to Nasser's 1956 nationalization of the Suez Canal.</t>
+          <t>U.S. State Department records documenting Gamal Abdel Nasser's 1956 nationalization of the Suez Canal and the resulting crisis.</t>
         </is>
       </c>
       <c r="P147" s="2" t="inlineStr">
@@ -14205,7 +14217,11 @@
           <t>SSP.01; SSP.02; SSP.05</t>
         </is>
       </c>
-      <c r="R147" s="2" t="inlineStr"/>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>Replaces a 1956 press photograph (copyright not guaranteed) with public-domain FRUS records on Nasser and the Suez Crisis, fitting W.69's focus on nationalist leaders such as Nasser.</t>
+        </is>
+      </c>
       <c r="S147" s="3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -14801,32 +14817,30 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Breakup of Yugoslavia / Bosnian War, 1990s</t>
+          <t>The Dayton Peace Accords, 1995 (General Framework Agreement for Peace in Bosnia and Herzegovina)</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>agreement (text)</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>U.S. military / press</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>1992-1995</t>
-        </is>
+          <t>U.S.-brokered; U.S. Department of State</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>1995</v>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Archives (NARA)</t>
+          <t>U.S. Department of State (state.gov)</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work / official agreement text</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -14836,7 +14850,7 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=Bosnia+war+Yugoslavia+breakup+1990s</t>
+          <t>https://www.state.gov/search/?q=Dayton+Accords+Bosnia+1995</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
@@ -14846,12 +14860,12 @@
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>The breakup of Yugoslavia, 1990s. U.S. National Archives.</t>
+          <t>General Framework Agreement for Peace in Bosnia and Herzegovina (Dayton Accords), 1995. U.S. Department of State.</t>
         </is>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>Photograph from the Yugoslav Wars in the Balkans.</t>
+          <t>Text of the 1995 Dayton Accords that ended the Bosnian War and established the postwar Balkan states.</t>
         </is>
       </c>
       <c r="P154" s="2" t="inlineStr">
@@ -14866,7 +14880,7 @@
       </c>
       <c r="R154" s="2" t="inlineStr">
         <is>
-          <t>Verify individual item rights (DoD imagery is PD).</t>
+          <t>Replaces a 1990s Bosnian War photograph (copyright not guaranteed) with the public-domain, U.S.-brokered Dayton Accords text, fitting W.73's focus on conflict and the establishment of new Balkan states.</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr">
@@ -15181,32 +15195,30 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>German reunification and the fall of the Berlin Wall, 1989-90</t>
+          <t>Treaty on the Final Settlement with Respect to Germany (Two Plus Four Treaty), 1990</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>treaty (text)</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>U.S. government / press</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>1989-1990</t>
-        </is>
+          <t>FRG, GDR, U.S., U.K., France, U.S.S.R.</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>1990</v>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>U.S. National Archives (NARA)</t>
+          <t>U.S. Department of State / Office of the Historian</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — treaty text</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -15216,7 +15228,7 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>https://catalog.archives.gov/search?q=German+reunification+1990+Berlin+Wall</t>
+          <t>https://history.state.gov/historicaldocuments/search?q=Final+Settlement+Germany+1990+Two+Plus+Four</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
@@ -15226,12 +15238,12 @@
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>German reunification, 1989-90. U.S. National Archives.</t>
+          <t>Treaty on the Final Settlement with Respect to Germany (Two Plus Four Treaty), September 12, 1990. Office of the Historian, U.S. Dept. of State.</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>Photograph of Germans celebrating reunification at the Brandenburg Gate.</t>
+          <t>Text of the 1990 Two Plus Four Treaty that ended four-power rights and enabled German reunification.</t>
         </is>
       </c>
       <c r="P158" s="2" t="inlineStr">
@@ -15246,7 +15258,7 @@
       </c>
       <c r="R158" s="2" t="inlineStr">
         <is>
-          <t>Verify individual item rights.</t>
+          <t>Replaces a 1989-90 reunification photograph (copyright not guaranteed) with the public-domain treaty text that legally effected German reunification, fitting W.75.</t>
         </is>
       </c>
       <c r="S158" s="3" t="inlineStr">
@@ -16024,32 +16036,32 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Medical and computing breakthroughs (vaccine, personal computer)</t>
+          <t>U.S. Public Health Service records and photographs of the polio vaccine, 1950s</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Photograph / artifact</t>
+          <t>Photograph / government record</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>U.S. government / Smithsonian</t>
+          <t>U.S. Public Health Service / CDC</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>20th c.</t>
+          <t>1950s</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>Smithsonian Institution</t>
+          <t>U.S. National Archives (NARA) / CDC Public Health Image Library</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -16059,7 +16071,7 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=personal+computer+polio+vaccine+20th+century</t>
+          <t>https://catalog.archives.gov/search?q=polio+vaccine+Public+Health+Service+1955</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
@@ -16069,12 +16081,12 @@
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>Modern medical and computing breakthroughs. Smithsonian Institution.</t>
+          <t>U.S. Public Health Service records and photographs of the polio vaccine, 1950s. U.S. National Archives / CDC.</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>Photograph of a landmark vaccine or early personal computer.</t>
+          <t>U.S. government photographs and records documenting the development and mass administration of the polio vaccine.</t>
         </is>
       </c>
       <c r="P167" s="2" t="inlineStr">
@@ -16087,7 +16099,11 @@
           <t>SSP.01; SSP.02</t>
         </is>
       </c>
-      <c r="R167" s="2" t="inlineStr"/>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>Replaces Smithsonian artifact/photographs of uncertain rights with public-domain U.S. government (PHS/CDC) records of a landmark medical breakthrough, fitting W.79.</t>
+        </is>
+      </c>
       <c r="S167" s="3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -16497,7 +16513,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Containerized shipping and global ports</t>
+          <t>U.S. Maritime Administration photographs of container shipping and ports</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -16507,7 +16523,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>U.S. government / Smithsonian</t>
+          <t>U.S. Department of Transportation, Maritime Administration</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -16517,12 +16533,12 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Smithsonian Institution</t>
+          <t>U.S. National Archives (NARA)</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -16532,7 +16548,7 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=container+ship+port+containerization</t>
+          <t>https://catalog.archives.gov/search?q=Maritime+Administration+container+ship+port</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
@@ -16542,12 +16558,12 @@
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>Containerized shipping. Smithsonian Institution.</t>
+          <t>U.S. Maritime Administration photographs of containerized shipping. U.S. National Archives.</t>
         </is>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>Photograph of container ships and cranes at a global port.</t>
+          <t>U.S. government photographs of container ships and port cranes illustrating containerization and global trade.</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
@@ -16560,7 +16576,11 @@
           <t>SSP.01; SSP.02; SSP.06</t>
         </is>
       </c>
-      <c r="R172" s="2" t="inlineStr"/>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>Replaces a Smithsonian shipping photograph of uncertain rights with public-domain U.S. government (MARAD) photographs of containerization for W.82.</t>
+        </is>
+      </c>
       <c r="S172" s="3" t="inlineStr">
         <is>
           <t>OK</t>
@@ -16590,32 +16610,32 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Early computer networking / the Internet</t>
+          <t>DARPA and NSF records and diagrams of the ARPANET and early Internet</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Photograph / artifact</t>
+          <t>Government record / diagram</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>U.S. government / Smithsonian</t>
+          <t>U.S. Defense Advanced Research Projects Agency / National Science Foundation</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>late 20th c.</t>
+          <t>1969-1990</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Smithsonian Institution</t>
+          <t>U.S. National Archives (NARA) / National Science Foundation</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -16625,7 +16645,7 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=ARPANET+early+internet+computer+networking</t>
+          <t>https://catalog.archives.gov/search?q=ARPANET+DARPA+network+diagram</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
@@ -16635,12 +16655,12 @@
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>Early computer networking. Smithsonian Institution.</t>
+          <t>DARPA/NSF records and network diagrams of the ARPANET and early Internet, 1969-1990. U.S. National Archives / NSF.</t>
         </is>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>Photograph of early networked computers / Internet hardware.</t>
+          <t>U.S. government ARPANET network diagrams documenting the origins of the Internet.</t>
         </is>
       </c>
       <c r="P173" s="2" t="inlineStr">
@@ -16655,7 +16675,7 @@
       </c>
       <c r="R173" s="2" t="inlineStr">
         <is>
-          <t>Verify individual item rights.</t>
+          <t>Replaces a Smithsonian networking photograph of uncertain rights with public-domain U.S. government (DARPA/NSF) ARPANET records and diagrams for W.82's computer-technology focus.</t>
         </is>
       </c>
       <c r="S173" s="3" t="inlineStr">
@@ -16966,17 +16986,17 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>The European Union / Maastricht and Rome treaties</t>
+          <t>U.S. government records on European integration and the European Union (FRUS and CIA reports)</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>Photograph / document</t>
+          <t>government document collection</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>European institutions; U.S. government</t>
+          <t>U.S. Department of State / Central Intelligence Agency</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -16986,12 +17006,12 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>U.S. Dept. of State, Office of the Historian</t>
+          <t>Office of the Historian, U.S. Department of State / CIA FOIA Reading Room</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -17001,7 +17021,7 @@
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>https://history.state.gov/search?q=European+Union+European+integration+treaty</t>
+          <t>https://history.state.gov/historicaldocuments/search?q=European+integration+European+Community</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
@@ -17011,12 +17031,12 @@
       </c>
       <c r="N177" s="2" t="inlineStr">
         <is>
-          <t>European integration and the EU. Office of the Historian, U.S. Dept. of State.</t>
+          <t>U.S. State Department (FRUS) and CIA records on European integration and the European Union, 1957-1993. Office of the Historian / CIA.</t>
         </is>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
-          <t>Document/photograph on the founding of the European Union.</t>
+          <t>U.S. government diplomatic records and intelligence reports analyzing European integration and the founding of the European Union.</t>
         </is>
       </c>
       <c r="P177" s="2" t="inlineStr">
@@ -17031,7 +17051,7 @@
       </c>
       <c r="R177" s="2" t="inlineStr">
         <is>
-          <t>Verify PD host for EU-origin documents.</t>
+          <t>Replaces EU-origin treaty documents (which carry EU reuse terms rather than full public domain) with public-domain U.S. government records on European integration, fitting W.84's supranational-organizations focus.</t>
         </is>
       </c>
       <c r="S177" s="3" t="inlineStr">
@@ -17063,32 +17083,32 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Industrialization of East Asia (Japan, "Asian Tigers," China)</t>
+          <t>U.S. government data and reports on South and East Asian economic growth</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>Data / government report</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>U.S. government / Smithsonian</t>
+          <t>U.S. Census Bureau / Bureau of Economic Analysis / International Trade Administration</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>late 20th c.</t>
+          <t>late 20th-21st c.</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>Smithsonian Institution</t>
+          <t>U.S. Census Bureau (census.gov)</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -17098,7 +17118,7 @@
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>https://www.si.edu/search?edan_q=East+Asia+industrialization+economy+Japan</t>
+          <t>https://www.census.gov/foreign-trade/balance/index.html</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
@@ -17108,12 +17128,12 @@
       </c>
       <c r="N178" s="2" t="inlineStr">
         <is>
-          <t>Industrialization of East Asia. Smithsonian Institution.</t>
+          <t>U.S. government trade and economic-growth data for South and East Asian economies. U.S. Census Bureau / Bureau of Economic Analysis.</t>
         </is>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>Photograph of modern East Asian manufacturing/industry.</t>
+          <t>U.S. government data and charts showing the rising economic role of South and East Asian countries in the global economy.</t>
         </is>
       </c>
       <c r="P178" s="2" t="inlineStr">
@@ -17128,7 +17148,7 @@
       </c>
       <c r="R178" s="2" t="inlineStr">
         <is>
-          <t>Contemporary; verify individual item rights.</t>
+          <t>Replaces a Smithsonian industrialization photograph of uncertain rights with public-domain U.S. government economic data on Asian growth for W.85.</t>
         </is>
       </c>
       <c r="S178" s="3" t="inlineStr">
@@ -17253,32 +17273,32 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Persian Gulf oil industry</t>
+          <t>U.S. Energy Information Administration data and maps of Persian Gulf oil production and reserves</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>Photograph</t>
+          <t>Data / map</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>U.S. government / press</t>
+          <t>U.S. Energy Information Administration</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>20th c.</t>
+          <t>20th-21st c.</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>Library of Congress</t>
+          <t>U.S. Energy Information Administration (eia.gov)</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>Public domain — verify individual item at repository</t>
+          <t>Public domain — U.S. government work</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
@@ -17288,7 +17308,7 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>https://www.loc.gov/search/?q=Persian+Gulf+oil+field+Saudi+Arabia+industry</t>
+          <t>https://www.eia.gov/international/analysis/special-topics/Persian_Gulf</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
@@ -17298,12 +17318,12 @@
       </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
-          <t>The Persian Gulf oil industry. Library of Congress.</t>
+          <t>U.S. Energy Information Administration, data and maps on Persian Gulf oil production and reserves. eia.gov.</t>
         </is>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>Photograph of oil derricks and refineries in the Persian Gulf.</t>
+          <t>U.S. government energy data and maps showing the oil production and reserves of the Persian Gulf states.</t>
         </is>
       </c>
       <c r="P180" s="2" t="inlineStr">
@@ -17318,7 +17338,7 @@
       </c>
       <c r="R180" s="2" t="inlineStr">
         <is>
-          <t>Verify individual item rights.</t>
+          <t>Replaces a 20th-century oil-industry photograph of uncertain rights with public-domain U.S. government (EIA) data and maps for W.86.</t>
         </is>
       </c>
       <c r="S180" s="3" t="inlineStr">
